--- a/PATXOT 512/Abril/PATXOT 521 ABRIL.xlsx
+++ b/PATXOT 512/Abril/PATXOT 521 ABRIL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B232002D-8967-47EA-A5DE-8D448BB3ACDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D35C9DA-6ED7-42AF-A4A9-0A425ADE1622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -425,12 +425,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="d/m"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="d/m"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1398,11 +1398,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1413,7 +1413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1436,14 +1436,14 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1460,7 +1460,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1468,10 +1468,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1480,7 +1480,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1493,7 +1493,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1506,7 +1506,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1533,8 +1533,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1542,8 +1542,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1554,11 +1554,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1569,7 +1569,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1603,12 +1603,12 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1638,16 +1638,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1657,7 +1657,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1668,6 +1668,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1730,7 +1733,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1745,12 +1748,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2205,7 +2204,7 @@
       <c r="B17" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="204">
+      <c r="C17" s="171">
         <v>88943.13</v>
       </c>
       <c r="D17" s="48"/>
@@ -2255,7 +2254,7 @@
         <v>126</v>
       </c>
       <c r="B23" s="92"/>
-      <c r="C23" s="203">
+      <c r="C23" s="85">
         <v>36534.6</v>
       </c>
       <c r="F23" s="22"/>
@@ -2277,9 +2276,7 @@
         <v>127</v>
       </c>
       <c r="B26" s="88"/>
-      <c r="C26" s="86">
-        <v>150000</v>
-      </c>
+      <c r="C26" s="86"/>
       <c r="D26" s="5"/>
       <c r="E26" s="14"/>
       <c r="F26" s="22"/>
@@ -2289,7 +2286,7 @@
       <c r="B27" s="90"/>
       <c r="C27" s="61">
         <f>SUM(C21:C26)</f>
-        <v>216534.6</v>
+        <v>66534.600000000006</v>
       </c>
       <c r="F27" s="22"/>
     </row>
@@ -2300,7 +2297,7 @@
       <c r="B28" s="80"/>
       <c r="C28" s="93">
         <f>+C27+C20</f>
-        <v>305477.73</v>
+        <v>155477.73000000001</v>
       </c>
       <c r="F28" s="22"/>
     </row>
@@ -2355,7 +2352,7 @@
       <c r="B37" s="34"/>
       <c r="C37" s="35">
         <f>+C35+C28</f>
-        <v>305477.73</v>
+        <v>155477.73000000001</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2372,7 +2369,7 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="146">
-        <v>-225247.17452636751</v>
+        <v>3596.7537403397146</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -2383,7 +2380,7 @@
       </c>
       <c r="C41" s="32">
         <f>'prorrateo '!F15</f>
-        <v>234321.66826670722</v>
+        <v>155477.74000000002</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
@@ -2405,7 +2402,7 @@
       </c>
       <c r="C43" s="94">
         <f>-(C28-C26)</f>
-        <v>-155477.72999999998</v>
+        <v>-155477.73000000001</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2415,7 +2412,7 @@
       <c r="B44" s="33"/>
       <c r="C44" s="40">
         <f>SUM(C40:C43)</f>
-        <v>-146403.23625966028</v>
+        <v>3596.7637403397239</v>
       </c>
       <c r="D44" s="6"/>
     </row>
@@ -2533,7 +2530,7 @@
         <v>49</v>
       </c>
       <c r="E1" s="50">
-        <v>291359.89</v>
+        <v>155477.73000000001</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2554,14 +2551,14 @@
       <c r="L2" s="103"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="179" t="s">
+      <c r="A3" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="180"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="181"/>
+      <c r="C3" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="177" t="s">
+      <c r="D3" s="178" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2570,19 +2567,19 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="175" t="s">
+      <c r="G3" s="176" t="s">
         <v>54</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="173" t="s">
+      <c r="I3" s="174" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="183" t="s">
+      <c r="J3" s="184" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="175" t="s">
+      <c r="K3" s="176" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="45" t="s">
@@ -2590,42 +2587,42 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="181"/>
-      <c r="B4" s="182"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="178"/>
+      <c r="A4" s="182"/>
+      <c r="B4" s="183"/>
+      <c r="C4" s="177"/>
+      <c r="D4" s="179"/>
       <c r="E4" s="58" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="176"/>
+      <c r="G4" s="177"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="174"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="176"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="185"/>
+      <c r="K4" s="177"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="171">
+      <c r="A5" s="172">
         <v>1</v>
       </c>
-      <c r="B5" s="172"/>
+      <c r="B5" s="173"/>
       <c r="C5" s="111" t="s">
         <v>66</v>
       </c>
       <c r="D5" s="59"/>
       <c r="E5" s="150">
-        <v>31310.712786555188</v>
+        <v>21455.92812</v>
       </c>
       <c r="F5" s="151">
         <f t="shared" ref="F5:F9" si="0">E5</f>
-        <v>31310.712786555188</v>
+        <v>21455.92812</v>
       </c>
       <c r="G5" s="152">
         <f>E5-F5</f>
@@ -2640,7 +2637,7 @@
       </c>
       <c r="J5" s="97">
         <f>E$1*I5/100</f>
-        <v>40207.664820000005</v>
+        <v>21455.926740000003</v>
       </c>
       <c r="K5" s="143">
         <f>edesur!H5</f>
@@ -2648,14 +2645,14 @@
       </c>
       <c r="L5" s="104">
         <f>G5+H5+J5+K5</f>
-        <v>40207.664820000005</v>
+        <v>21455.926740000003</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="171">
+      <c r="A6" s="172">
         <v>2</v>
       </c>
-      <c r="B6" s="172"/>
+      <c r="B6" s="173"/>
       <c r="C6" s="111" t="s">
         <v>67</v>
       </c>
@@ -2663,11 +2660,11 @@
         <v>72</v>
       </c>
       <c r="E6" s="150">
-        <v>30871.318343297658</v>
+        <v>18439.659963999999</v>
       </c>
       <c r="F6" s="151">
         <f t="shared" si="0"/>
-        <v>30871.318343297658</v>
+        <v>18439.659963999999</v>
       </c>
       <c r="G6" s="152">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
@@ -2682,7 +2679,7 @@
       </c>
       <c r="J6" s="97">
         <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
-        <v>34555.282954000002</v>
+        <v>18439.658778000001</v>
       </c>
       <c r="K6" s="143">
         <f>edesur!H6</f>
@@ -2690,14 +2687,14 @@
       </c>
       <c r="L6" s="104">
         <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
-        <v>34555.282954000002</v>
+        <v>18439.658778000001</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="171">
+      <c r="A7" s="172">
         <v>3</v>
       </c>
-      <c r="B7" s="172"/>
+      <c r="B7" s="173"/>
       <c r="C7" s="111" t="s">
         <v>67</v>
       </c>
@@ -2705,11 +2702,11 @@
         <v>73</v>
       </c>
       <c r="E7" s="150">
-        <v>31575.545756876258</v>
+        <v>19372.526404</v>
       </c>
       <c r="F7" s="151">
         <f t="shared" si="0"/>
-        <v>31575.545756876258</v>
+        <v>19372.526404</v>
       </c>
       <c r="G7" s="152">
         <f t="shared" si="1"/>
@@ -2724,7 +2721,7 @@
       </c>
       <c r="J7" s="97">
         <f t="shared" si="3"/>
-        <v>36303.442294000008</v>
+        <v>19372.525158</v>
       </c>
       <c r="K7" s="143">
         <f>edesur!H7</f>
@@ -2732,14 +2729,14 @@
       </c>
       <c r="L7" s="104">
         <f t="shared" si="4"/>
-        <v>36303.442294000008</v>
+        <v>19372.525158</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="171">
+      <c r="A8" s="172">
         <v>4</v>
       </c>
-      <c r="B8" s="172"/>
+      <c r="B8" s="173"/>
       <c r="C8" s="111" t="s">
         <v>68</v>
       </c>
@@ -2747,11 +2744,11 @@
         <v>74</v>
       </c>
       <c r="E8" s="150">
-        <v>36252.089402090307</v>
+        <v>22932.966650000002</v>
       </c>
       <c r="F8" s="151">
         <f t="shared" si="0"/>
-        <v>36252.089402090307</v>
+        <v>22932.966650000002</v>
       </c>
       <c r="G8" s="152">
         <f t="shared" si="1"/>
@@ -2766,7 +2763,7 @@
       </c>
       <c r="J8" s="97">
         <f t="shared" si="3"/>
-        <v>42975.583775000006</v>
+        <v>22932.965175000001</v>
       </c>
       <c r="K8" s="143">
         <f>edesur!H8</f>
@@ -2774,14 +2771,14 @@
       </c>
       <c r="L8" s="104">
         <f t="shared" si="4"/>
-        <v>42975.583775000006</v>
+        <v>22932.965175000001</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="171">
+      <c r="A9" s="172">
         <v>5</v>
       </c>
-      <c r="B9" s="172"/>
+      <c r="B9" s="173"/>
       <c r="C9" s="111" t="s">
         <v>69</v>
       </c>
@@ -2789,11 +2786,11 @@
         <v>75</v>
       </c>
       <c r="E9" s="150">
-        <v>26179.162034284283</v>
+        <v>19294.787533999999</v>
       </c>
       <c r="F9" s="151">
         <f t="shared" si="0"/>
-        <v>26179.162034284283</v>
+        <v>19294.787533999999</v>
       </c>
       <c r="G9" s="152">
         <f t="shared" si="1"/>
@@ -2808,7 +2805,7 @@
       </c>
       <c r="J9" s="97">
         <f t="shared" si="3"/>
-        <v>36157.762348999997</v>
+        <v>19294.786293000001</v>
       </c>
       <c r="K9" s="143">
         <f>edesur!H9</f>
@@ -2816,24 +2813,24 @@
       </c>
       <c r="L9" s="104">
         <f>G9+H9+J9+K9</f>
-        <v>36157.762348999997</v>
+        <v>19294.786293000001</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="171">
+      <c r="A10" s="172">
         <v>6</v>
       </c>
-      <c r="B10" s="172"/>
+      <c r="B10" s="173"/>
       <c r="C10" s="111" t="s">
         <v>70</v>
       </c>
       <c r="D10" s="73"/>
       <c r="E10" s="150">
-        <v>26422.052583705688</v>
+        <v>19403.621952000001</v>
       </c>
       <c r="F10" s="151">
         <f>E10</f>
-        <v>26422.052583705688</v>
+        <v>19403.621952000001</v>
       </c>
       <c r="G10" s="152">
         <f t="shared" si="1"/>
@@ -2848,7 +2845,7 @@
       </c>
       <c r="J10" s="97">
         <f t="shared" si="3"/>
-        <v>36361.714272000005</v>
+        <v>19403.620704000001</v>
       </c>
       <c r="K10" s="143">
         <f>edesur!H10</f>
@@ -2856,24 +2853,24 @@
       </c>
       <c r="L10" s="104">
         <f t="shared" si="4"/>
-        <v>36361.714272000005</v>
+        <v>19403.620704000001</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="171">
+      <c r="A11" s="172">
         <v>7</v>
       </c>
-      <c r="B11" s="172"/>
+      <c r="B11" s="173"/>
       <c r="C11" s="111" t="s">
         <v>71</v>
       </c>
       <c r="D11" s="73"/>
       <c r="E11" s="150">
-        <v>39198.725671190645</v>
+        <v>28390.235323999997</v>
       </c>
       <c r="F11" s="151">
         <f>E11</f>
-        <v>39198.725671190645</v>
+        <v>28390.235323999997</v>
       </c>
       <c r="G11" s="152">
         <f t="shared" si="1"/>
@@ -2888,7 +2885,7 @@
       </c>
       <c r="J11" s="97">
         <f t="shared" si="3"/>
-        <v>53202.315914000006</v>
+        <v>28390.233498000005</v>
       </c>
       <c r="K11" s="143">
         <f>edesur!H11</f>
@@ -2896,25 +2893,25 @@
       </c>
       <c r="L11" s="104">
         <f t="shared" si="4"/>
-        <v>53202.315914000006</v>
+        <v>28390.233498000005</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="171" t="s">
+      <c r="A12" s="172" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="172"/>
+      <c r="B12" s="173"/>
       <c r="C12" s="111" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="73"/>
       <c r="E12" s="150">
-        <v>4212.6036841376008</v>
+        <v>2083.4017159999999</v>
       </c>
       <c r="F12" s="151">
         <f t="shared" ref="F12:F14" si="5">E12</f>
-        <v>4212.6036841376008</v>
+        <v>2083.4017159999999</v>
       </c>
       <c r="G12" s="152">
         <f t="shared" si="1"/>
@@ -2929,32 +2926,32 @@
       </c>
       <c r="J12" s="97">
         <f t="shared" si="3"/>
-        <v>3904.2225260000005</v>
+        <v>2083.4015820000004</v>
       </c>
       <c r="K12" s="143">
         <v>0</v>
       </c>
       <c r="L12" s="104">
         <f t="shared" si="4"/>
-        <v>3904.2225260000005</v>
+        <v>2083.4015820000004</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="171" t="s">
+      <c r="A13" s="172" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="172"/>
+      <c r="B13" s="173"/>
       <c r="C13" s="111" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="73"/>
       <c r="E13" s="150">
-        <v>4149.7290022848001</v>
+        <v>2052.3061680000001</v>
       </c>
       <c r="F13" s="151">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
+        <v>2052.3061680000001</v>
       </c>
       <c r="G13" s="152">
         <f t="shared" si="1"/>
@@ -2969,32 +2966,32 @@
       </c>
       <c r="J13" s="97">
         <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3060360000004</v>
       </c>
       <c r="K13" s="143">
         <v>0</v>
       </c>
       <c r="L13" s="104">
         <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3060360000004</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="172"/>
+      <c r="B14" s="173"/>
       <c r="C14" s="59" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="73"/>
       <c r="E14" s="150">
-        <v>4149.7290022848001</v>
+        <v>2052.3061680000001</v>
       </c>
       <c r="F14" s="151">
         <f t="shared" si="5"/>
-        <v>4149.7290022848001</v>
+        <v>2052.3061680000001</v>
       </c>
       <c r="G14" s="152">
         <f t="shared" si="1"/>
@@ -3009,14 +3006,14 @@
       </c>
       <c r="J14" s="97">
         <f t="shared" si="3"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3060360000004</v>
       </c>
       <c r="K14" s="143">
         <v>0</v>
       </c>
       <c r="L14" s="104">
         <f t="shared" si="4"/>
-        <v>3845.9505480000003</v>
+        <v>2052.3060360000004</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3028,11 +3025,11 @@
       <c r="D15" s="107"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>234321.66826670722</v>
+        <v>155477.74000000002</v>
       </c>
       <c r="F15" s="108">
         <f>SUM(F5:F14)</f>
-        <v>234321.66826670722</v>
+        <v>155477.74000000002</v>
       </c>
       <c r="G15" s="108"/>
       <c r="H15" s="109">
@@ -3045,7 +3042,7 @@
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>291359.89</v>
+        <v>155477.73000000001</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
@@ -3053,7 +3050,7 @@
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>291359.89</v>
+        <v>155477.73000000001</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
@@ -3445,15 +3442,15 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="185" t="s">
+      <c r="E32" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="186"/>
-      <c r="G32" s="186"/>
-      <c r="H32" s="186"/>
-      <c r="I32" s="186"/>
-      <c r="J32" s="186"/>
-      <c r="K32" s="187"/>
+      <c r="F32" s="187"/>
+      <c r="G32" s="187"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="187"/>
+      <c r="K32" s="188"/>
       <c r="L32" s="153"/>
       <c r="M32" s="154"/>
       <c r="N32"/>
@@ -3461,15 +3458,15 @@
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="188" t="s">
+      <c r="E33" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="186"/>
-      <c r="G33" s="186"/>
-      <c r="H33" s="186"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="186"/>
-      <c r="K33" s="187"/>
+      <c r="F33" s="187"/>
+      <c r="G33" s="187"/>
+      <c r="H33" s="187"/>
+      <c r="I33" s="187"/>
+      <c r="J33" s="187"/>
+      <c r="K33" s="188"/>
       <c r="L33" s="155"/>
       <c r="M33" s="156"/>
       <c r="N33"/>
@@ -3524,15 +3521,15 @@
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="189" t="s">
+      <c r="E37" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="190"/>
-      <c r="G37" s="190"/>
-      <c r="H37" s="190"/>
-      <c r="I37" s="190"/>
-      <c r="J37" s="190"/>
-      <c r="K37" s="191"/>
+      <c r="F37" s="191"/>
+      <c r="G37" s="191"/>
+      <c r="H37" s="191"/>
+      <c r="I37" s="191"/>
+      <c r="J37" s="191"/>
+      <c r="K37" s="192"/>
       <c r="L37" s="155"/>
       <c r="M37" s="156"/>
       <c r="N37"/>
@@ -3570,10 +3567,10 @@
         <v>45674</v>
       </c>
       <c r="K39" s="156"/>
-      <c r="L39" s="192" t="s">
+      <c r="L39" s="193" t="s">
         <v>118</v>
       </c>
-      <c r="M39" s="193"/>
+      <c r="M39" s="194"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
@@ -3604,8 +3601,8 @@
       <c r="I41" s="158"/>
       <c r="J41" s="158"/>
       <c r="K41" s="156"/>
-      <c r="L41" s="194"/>
-      <c r="M41" s="193"/>
+      <c r="L41" s="195"/>
+      <c r="M41" s="194"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
@@ -3620,7 +3617,7 @@
       <c r="I42" s="158"/>
       <c r="J42" s="164">
         <f>J7</f>
-        <v>36303.442294000008</v>
+        <v>19372.525158</v>
       </c>
       <c r="K42" s="156"/>
       <c r="L42" s="155"/>
@@ -3770,18 +3767,18 @@
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="195" t="s">
+      <c r="E52" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="196"/>
-      <c r="G52" s="196"/>
-      <c r="H52" s="196"/>
-      <c r="I52" s="196"/>
-      <c r="J52" s="197">
+      <c r="F52" s="197"/>
+      <c r="G52" s="197"/>
+      <c r="H52" s="197"/>
+      <c r="I52" s="197"/>
+      <c r="J52" s="198">
         <f>SUM(J42:J51)</f>
-        <v>36379.242294000011</v>
-      </c>
-      <c r="K52" s="187"/>
+        <v>19448.325158000003</v>
+      </c>
+      <c r="K52" s="188"/>
       <c r="L52" s="168"/>
       <c r="M52" s="169"/>
       <c r="N52"/>
@@ -3793,28 +3790,28 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="185" t="s">
+      <c r="E56" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="186"/>
-      <c r="G56" s="186"/>
-      <c r="H56" s="186"/>
-      <c r="I56" s="186"/>
-      <c r="J56" s="186"/>
-      <c r="K56" s="187"/>
+      <c r="F56" s="187"/>
+      <c r="G56" s="187"/>
+      <c r="H56" s="187"/>
+      <c r="I56" s="187"/>
+      <c r="J56" s="187"/>
+      <c r="K56" s="188"/>
       <c r="L56" s="153"/>
       <c r="M56" s="154"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="188" t="s">
+      <c r="E57" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="186"/>
-      <c r="G57" s="186"/>
-      <c r="H57" s="186"/>
-      <c r="I57" s="186"/>
-      <c r="J57" s="186"/>
-      <c r="K57" s="187"/>
+      <c r="F57" s="187"/>
+      <c r="G57" s="187"/>
+      <c r="H57" s="187"/>
+      <c r="I57" s="187"/>
+      <c r="J57" s="187"/>
+      <c r="K57" s="188"/>
       <c r="L57" s="155"/>
       <c r="M57" s="156"/>
     </row>
@@ -3857,15 +3854,15 @@
       <c r="M60" s="156"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="189" t="s">
+      <c r="E61" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="F61" s="190"/>
-      <c r="G61" s="190"/>
-      <c r="H61" s="190"/>
-      <c r="I61" s="190"/>
-      <c r="J61" s="190"/>
-      <c r="K61" s="191"/>
+      <c r="F61" s="191"/>
+      <c r="G61" s="191"/>
+      <c r="H61" s="191"/>
+      <c r="I61" s="191"/>
+      <c r="J61" s="191"/>
+      <c r="K61" s="192"/>
       <c r="L61" s="155"/>
       <c r="M61" s="156"/>
     </row>
@@ -3897,10 +3894,10 @@
         <v>45674</v>
       </c>
       <c r="K63" s="156"/>
-      <c r="L63" s="192" t="s">
+      <c r="L63" s="193" t="s">
         <v>118</v>
       </c>
-      <c r="M63" s="193"/>
+      <c r="M63" s="194"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="155" t="s">
@@ -3925,8 +3922,8 @@
       <c r="I65" s="158"/>
       <c r="J65" s="158"/>
       <c r="K65" s="156"/>
-      <c r="L65" s="194"/>
-      <c r="M65" s="193"/>
+      <c r="L65" s="195"/>
+      <c r="M65" s="194"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="155" t="s">
@@ -3938,7 +3935,7 @@
       <c r="I66" s="158"/>
       <c r="J66" s="164">
         <f>J8</f>
-        <v>42975.583775000006</v>
+        <v>22932.965175000001</v>
       </c>
       <c r="K66" s="156"/>
       <c r="L66" s="155"/>
@@ -4053,45 +4050,45 @@
       <c r="M75" s="167"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="195" t="s">
+      <c r="E76" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="F76" s="196"/>
-      <c r="G76" s="196"/>
-      <c r="H76" s="196"/>
-      <c r="I76" s="196"/>
-      <c r="J76" s="197">
+      <c r="F76" s="197"/>
+      <c r="G76" s="197"/>
+      <c r="H76" s="197"/>
+      <c r="I76" s="197"/>
+      <c r="J76" s="198">
         <f>SUM(J66:J75)</f>
-        <v>42975.583775000006</v>
-      </c>
-      <c r="K76" s="187"/>
+        <v>22932.965175000001</v>
+      </c>
+      <c r="K76" s="188"/>
       <c r="L76" s="168"/>
       <c r="M76" s="169"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="185" t="s">
+      <c r="E83" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="F83" s="186"/>
-      <c r="G83" s="186"/>
-      <c r="H83" s="186"/>
-      <c r="I83" s="186"/>
-      <c r="J83" s="186"/>
-      <c r="K83" s="187"/>
+      <c r="F83" s="187"/>
+      <c r="G83" s="187"/>
+      <c r="H83" s="187"/>
+      <c r="I83" s="187"/>
+      <c r="J83" s="187"/>
+      <c r="K83" s="188"/>
       <c r="L83" s="153"/>
       <c r="M83" s="154"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="188" t="s">
+      <c r="E84" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="F84" s="186"/>
-      <c r="G84" s="186"/>
-      <c r="H84" s="186"/>
-      <c r="I84" s="186"/>
-      <c r="J84" s="186"/>
-      <c r="K84" s="187"/>
+      <c r="F84" s="187"/>
+      <c r="G84" s="187"/>
+      <c r="H84" s="187"/>
+      <c r="I84" s="187"/>
+      <c r="J84" s="187"/>
+      <c r="K84" s="188"/>
       <c r="L84" s="155"/>
       <c r="M84" s="156"/>
     </row>
@@ -4134,15 +4131,15 @@
       <c r="M87" s="156"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="189" t="s">
+      <c r="E88" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="F88" s="190"/>
-      <c r="G88" s="190"/>
-      <c r="H88" s="190"/>
-      <c r="I88" s="190"/>
-      <c r="J88" s="190"/>
-      <c r="K88" s="191"/>
+      <c r="F88" s="191"/>
+      <c r="G88" s="191"/>
+      <c r="H88" s="191"/>
+      <c r="I88" s="191"/>
+      <c r="J88" s="191"/>
+      <c r="K88" s="192"/>
       <c r="L88" s="155"/>
       <c r="M88" s="156"/>
     </row>
@@ -4174,10 +4171,10 @@
         <v>45674</v>
       </c>
       <c r="K90" s="156"/>
-      <c r="L90" s="192" t="s">
+      <c r="L90" s="193" t="s">
         <v>118</v>
       </c>
-      <c r="M90" s="193"/>
+      <c r="M90" s="194"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="155" t="s">
@@ -4202,8 +4199,8 @@
       <c r="I92" s="158"/>
       <c r="J92" s="158"/>
       <c r="K92" s="156"/>
-      <c r="L92" s="194"/>
-      <c r="M92" s="193"/>
+      <c r="L92" s="195"/>
+      <c r="M92" s="194"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="155" t="s">
@@ -4215,7 +4212,7 @@
       <c r="I93" s="158"/>
       <c r="J93" s="164">
         <f>J10</f>
-        <v>36361.714272000005</v>
+        <v>19403.620704000001</v>
       </c>
       <c r="K93" s="156"/>
       <c r="L93" s="155"/>
@@ -4329,45 +4326,45 @@
       <c r="M102" s="167"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="195" t="s">
+      <c r="E103" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="F103" s="196"/>
-      <c r="G103" s="196"/>
-      <c r="H103" s="196"/>
-      <c r="I103" s="196"/>
-      <c r="J103" s="197">
+      <c r="F103" s="197"/>
+      <c r="G103" s="197"/>
+      <c r="H103" s="197"/>
+      <c r="I103" s="197"/>
+      <c r="J103" s="198">
         <f>SUM(J93:J102)</f>
-        <v>36385.604272000004</v>
-      </c>
-      <c r="K103" s="187"/>
+        <v>19427.510704</v>
+      </c>
+      <c r="K103" s="188"/>
       <c r="L103" s="168"/>
       <c r="M103" s="169"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="185" t="s">
+      <c r="E108" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="F108" s="186"/>
-      <c r="G108" s="186"/>
-      <c r="H108" s="186"/>
-      <c r="I108" s="186"/>
-      <c r="J108" s="186"/>
-      <c r="K108" s="187"/>
+      <c r="F108" s="187"/>
+      <c r="G108" s="187"/>
+      <c r="H108" s="187"/>
+      <c r="I108" s="187"/>
+      <c r="J108" s="187"/>
+      <c r="K108" s="188"/>
       <c r="L108" s="153"/>
       <c r="M108" s="154"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="188" t="s">
+      <c r="E109" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="F109" s="186"/>
-      <c r="G109" s="186"/>
-      <c r="H109" s="186"/>
-      <c r="I109" s="186"/>
-      <c r="J109" s="186"/>
-      <c r="K109" s="187"/>
+      <c r="F109" s="187"/>
+      <c r="G109" s="187"/>
+      <c r="H109" s="187"/>
+      <c r="I109" s="187"/>
+      <c r="J109" s="187"/>
+      <c r="K109" s="188"/>
       <c r="L109" s="155"/>
       <c r="M109" s="156"/>
     </row>
@@ -4410,15 +4407,15 @@
       <c r="M112" s="156"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="189" t="s">
+      <c r="E113" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="F113" s="190"/>
-      <c r="G113" s="190"/>
-      <c r="H113" s="190"/>
-      <c r="I113" s="190"/>
-      <c r="J113" s="190"/>
-      <c r="K113" s="191"/>
+      <c r="F113" s="191"/>
+      <c r="G113" s="191"/>
+      <c r="H113" s="191"/>
+      <c r="I113" s="191"/>
+      <c r="J113" s="191"/>
+      <c r="K113" s="192"/>
       <c r="L113" s="155"/>
       <c r="M113" s="156"/>
     </row>
@@ -4450,10 +4447,10 @@
         <v>45674</v>
       </c>
       <c r="K115" s="156"/>
-      <c r="L115" s="192" t="s">
+      <c r="L115" s="193" t="s">
         <v>118</v>
       </c>
-      <c r="M115" s="193"/>
+      <c r="M115" s="194"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="155" t="s">
@@ -4478,8 +4475,8 @@
       <c r="I117" s="158"/>
       <c r="J117" s="158"/>
       <c r="K117" s="156"/>
-      <c r="L117" s="194"/>
-      <c r="M117" s="193"/>
+      <c r="L117" s="195"/>
+      <c r="M117" s="194"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="155" t="s">
@@ -4491,7 +4488,7 @@
       <c r="I118" s="158"/>
       <c r="J118" s="164">
         <f>J5</f>
-        <v>40207.664820000005</v>
+        <v>21455.926740000003</v>
       </c>
       <c r="K118" s="156"/>
       <c r="L118" s="155"/>
@@ -4606,18 +4603,18 @@
       <c r="M127" s="167"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="195" t="s">
+      <c r="E128" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="F128" s="196"/>
-      <c r="G128" s="196"/>
-      <c r="H128" s="196"/>
-      <c r="I128" s="196"/>
-      <c r="J128" s="197">
+      <c r="F128" s="197"/>
+      <c r="G128" s="197"/>
+      <c r="H128" s="197"/>
+      <c r="I128" s="197"/>
+      <c r="J128" s="198">
         <f>SUM(J118:J127)</f>
-        <v>40155.324820000009</v>
-      </c>
-      <c r="K128" s="187"/>
+        <v>21403.586740000002</v>
+      </c>
+      <c r="K128" s="188"/>
       <c r="L128" s="168"/>
       <c r="M128" s="169"/>
     </row>
@@ -5224,11 +5221,11 @@
       <c r="D1" s="56">
         <v>50000</v>
       </c>
-      <c r="H1" s="202">
+      <c r="H1" s="203">
         <v>250000</v>
       </c>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="53" t="s">
@@ -5292,13 +5289,13 @@
         <v>54</v>
       </c>
       <c r="K4" s="68"/>
-      <c r="L4" s="200" t="s">
+      <c r="L4" s="201" t="s">
         <v>61</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="198" t="s">
+      <c r="N4" s="199" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="21"/>
@@ -5327,11 +5324,11 @@
         <v>60</v>
       </c>
       <c r="K5" s="58"/>
-      <c r="L5" s="201"/>
+      <c r="L5" s="202"/>
       <c r="M5" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="199"/>
+      <c r="N5" s="200"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
